--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:53:23+00:00</t>
+    <t>2026-09-18T08:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$71</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3253" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2756" uniqueCount="567">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:26:19+00:00</t>
+    <t>2026-09-24T07:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -491,7 +491,7 @@
 </t>
   </si>
   <si>
-    <t>Business Identifier for observation</t>
+    <t>Identifiant de l'exposition aux radiations</t>
   </si>
   <si>
     <t>A unique identifier assigned to this observation.</t>
@@ -500,41 +500,71 @@
     <t>Allows observations to be distinguished and referenced.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:type}
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>OBX.21  For OBX segments from systems without OBX-21 support a combination of ORC/OBR and OBX must be negotiated between trading partners to uniquely identify the OBX segment. Depending on how V2 has been implemented each of these may be an option: 1) OBR-3 + OBX-3 + OBX-4 or 2) OBR-3 + OBR-4 + OBX-3 + OBX-4 or 2) some other way to uniquely ID the OBR/ORC + OBX-3 + OBX-4.</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>Observation.basedOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fulfills
 </t>
   </si>
   <si>
-    <t>Identifiant de l'exposition aux radiations</t>
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Fulfills plan, proposal or order</t>
+  </si>
+  <si>
+    <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
+  </si>
+  <si>
+    <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
   </si>
   <si>
     <t>open</t>
   </si>
   <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>OBX.21  For OBX segments from systems without OBX-21 support a combination of ORC/OBR and OBX must be negotiated between trading partners to uniquely identify the OBX segment. Depending on how V2 has been implemented each of these may be an option: 1) OBR-3 + OBX-3 + OBX-4 or 2) OBR-3 + OBR-4 + OBX-3 + OBX-4 or 2) some other way to uniquely ID the OBR/ORC + OBX-3 + OBX-4.</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>Observation.identifier:radiationUID</t>
-  </si>
-  <si>
-    <t>radiationUID</t>
-  </si>
-  <si>
-    <t>Radiation Exposures UID</t>
-  </si>
-  <si>
-    <t>Observation.identifier:radiationUID.id</t>
-  </si>
-  <si>
-    <t>Observation.identifier.id</t>
+    <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>ORC</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=COMP].source[moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>Observation.basedOn:serviceRequestAccessionNumber</t>
+  </si>
+  <si>
+    <t>serviceRequestAccessionNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-service-request-imaging-document|0.1.0)
+</t>
+  </si>
+  <si>
+    <t>Référence à la demande d'examen contenant l'Accession Number</t>
+  </si>
+  <si>
+    <t>Observation.basedOn:serviceRequestAccessionNumber.id</t>
+  </si>
+  <si>
+    <t>Observation.basedOn.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -553,10 +583,10 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Observation.identifier:radiationUID.extension</t>
-  </si>
-  <si>
-    <t>Observation.identifier.extension</t>
+    <t>Observation.basedOn:serviceRequestAccessionNumber.extension</t>
+  </si>
+  <si>
+    <t>Observation.basedOn.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -572,92 +602,254 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Observation.identifier:radiationUID.use</t>
-  </si>
-  <si>
-    <t>Observation.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>Observation.basedOn:serviceRequestAccessionNumber.reference</t>
+  </si>
+  <si>
+    <t>Observation.basedOn.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>Observation.basedOn:serviceRequestAccessionNumber.type</t>
+  </si>
+  <si>
+    <t>Observation.basedOn.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>Observation.basedOn:serviceRequestAccessionNumber.identifier</t>
+  </si>
+  <si>
+    <t>Observation.basedOn.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-accession-number-identifier-document|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>Observation.basedOn:serviceRequestAccessionNumber.display</t>
+  </si>
+  <si>
+    <t>Observation.basedOn.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
+  </si>
+  <si>
+    <t>Observation.partOf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Container
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-administration-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-procedure-imaging-document|0.1.0)
+</t>
+  </si>
+  <si>
+    <t>Ressources liées à cette exposition aux radiations (administration de produits radiopharmaceutiques, techniques d'imagerie)</t>
+  </si>
+  <si>
+    <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
+  </si>
+  <si>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+  </si>
+  <si>
+    <t>Event.partOf</t>
+  </si>
+  <si>
+    <t>Varies by domain</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=FLFS].target</t>
+  </si>
+  <si>
+    <t>Observation.status</t>
+  </si>
+  <si>
+    <t>registered | preliminary | final | amended +</t>
+  </si>
+  <si>
+    <t>The status of the result value.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+  </si>
+  <si>
+    <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Observation.identifier:radiationUID.type</t>
-  </si>
-  <si>
-    <t>Observation.identifier.type</t>
+    <t>Codes providing the status of an observation.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>&lt; 445584004 |Report by finality status|</t>
+  </si>
+  <si>
+    <t>OBX-11</t>
+  </si>
+  <si>
+    <t>status  Amended &amp; Final are differentiated by whether it is the subject of a ControlAct event with a type of "revise"</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>Observation.category</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Observation.identifier:radiationUID.type.id</t>
-  </si>
-  <si>
-    <t>Observation.identifier.type.id</t>
-  </si>
-  <si>
-    <t>Observation.identifier:radiationUID.type.extension</t>
-  </si>
-  <si>
-    <t>Observation.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>Observation.identifier:radiationUID.type.coding</t>
-  </si>
-  <si>
-    <t>Observation.identifier.type.coding</t>
+    <t>Classification of  type of observation</t>
+  </si>
+  <si>
+    <t>A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
+    <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name
+</t>
+  </si>
+  <si>
+    <t>Type of observation (code / type)</t>
+  </si>
+  <si>
+    <t>Describes what was observed. Sometimes this is called the observation "name".</t>
+  </si>
+  <si>
+    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
+  </si>
+  <si>
+    <t>Observation.code.id</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
@@ -676,6 +868,10 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
+    <t>value:code}
+value:system}</t>
+  </si>
+  <si>
     <t>CodeableConcept.coding</t>
   </si>
   <si>
@@ -685,22 +881,28 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Observation.identifier:radiationUID.type.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.identifier:radiationUID.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.identifier:radiationUID.type.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.identifier.type.coding.system</t>
+    <t>Observation.code.coding:radiationDose</t>
+  </si>
+  <si>
+    <t>radiationDose</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:radiationDose.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:radiationDose.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:radiationDose.system</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.system</t>
   </si>
   <si>
     <t>Identity of the terminology system</t>
@@ -715,6 +917,9 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>http://loinc.org</t>
+  </si>
+  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -724,10 +929,10 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>Observation.identifier:radiationUID.type.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.identifier.type.coding.version</t>
+    <t>Observation.code.coding:radiationDose.version</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.version</t>
   </si>
   <si>
     <t>Version of the system - if relevant</t>
@@ -748,10 +953,10 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>Observation.identifier:radiationUID.type.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.identifier.type.coding.code</t>
+    <t>Observation.code.coding:radiationDose.code</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.code</t>
   </si>
   <si>
     <t>Symbol in syntax defined by the system</t>
@@ -763,7 +968,7 @@
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
-    <t>00083010</t>
+    <t>73569-6</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -775,10 +980,10 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Observation.identifier:radiationUID.type.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.identifier.type.coding.display</t>
+    <t>Observation.code.coding:radiationDose.display</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.display</t>
   </si>
   <si>
     <t>Representation defined by the system</t>
@@ -799,10 +1004,10 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Observation.identifier:radiationUID.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.identifier.type.coding.userSelected</t>
+    <t>Observation.code.coding:radiationDose.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.userSelected</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
@@ -830,10 +1035,7 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
-    <t>Observation.identifier:radiationUID.type.text</t>
-  </si>
-  <si>
-    <t>Observation.identifier.type.text</t>
+    <t>Observation.code.text</t>
   </si>
   <si>
     <t>Plain text representation of the concept</t>
@@ -857,506 +1059,171 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
-    <t>Observation.identifier:radiationUID.system</t>
-  </si>
-  <si>
-    <t>Observation.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>urn:dicom:uid</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>Observation.identifier:radiationUID.value</t>
-  </si>
-  <si>
-    <t>Observation.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>Observation.identifier:radiationUID.period</t>
-  </si>
-  <si>
-    <t>Observation.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
+    <t>Observation.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-document|0.1.0)
 </t>
   </si>
   <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>Observation.identifier:radiationUID.assigner</t>
-  </si>
-  <si>
-    <t>Observation.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t>Patient exposé aux radiations</t>
+  </si>
+  <si>
+    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+  </si>
+  <si>
+    <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
+  </si>
+  <si>
+    <t>Observations have no value if you don't know who or what they're about.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>PID-3</t>
+  </si>
+  <si>
+    <t>participation[typeCode=RTGT]</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>Observation.focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>Observation.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fulfills
+    <t>What the observation is about, when it is not about the subject of record</t>
+  </si>
+  <si>
+    <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
+  </si>
+  <si>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+  </si>
+  <si>
+    <t>participation[typeCode=SBJ]</t>
+  </si>
+  <si>
+    <t>Observation.encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Context
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
-    <t>Fulfills plan, proposal or order</t>
-  </si>
-  <si>
-    <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
-  </si>
-  <si>
-    <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
+    <t>Healthcare event during which this observation is made</t>
+  </si>
+  <si>
+    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+  </si>
+  <si>
+    <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
+  </si>
+  <si>
+    <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
+  </si>
+  <si>
+    <t>Event.context</t>
+  </si>
+  <si>
+    <t>PV1</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occurrence
 </t>
   </si>
   <si>
-    <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>ORC</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>Observation.basedOn:serviceRequestAccessionNumber</t>
-  </si>
-  <si>
-    <t>serviceRequestAccessionNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-service-request-imaging-document|0.1.0)
+    <t xml:space="preserve">dateTime
 </t>
   </si>
   <si>
-    <t>Référence à la demande d'examen contenant l'Accession Number</t>
-  </si>
-  <si>
-    <t>Observation.partOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Container
+    <t>Date de début de l'exposition aux radiations</t>
+  </si>
+  <si>
+    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
+  </si>
+  <si>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+  </si>
+  <si>
+    <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
+  </si>
+  <si>
+    <t>effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Observation.issued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
+    <t>Date/Time this version was made available</t>
+  </si>
+  <si>
+    <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
+  </si>
+  <si>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+  </si>
+  <si>
+    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
+  </si>
+  <si>
+    <t>participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>Observation.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
-    <t>Part of referenced event</t>
-  </si>
-  <si>
-    <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
-  </si>
-  <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>Who is responsible for the observation</t>
+  </si>
+  <si>
+    <t>Who was responsible for asserting the observed value as "true".</t>
+  </si>
+  <si>
+    <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
     <t xml:space="preserve">type:reference}
 </t>
   </si>
   <si>
-    <t>Ressources liées à cette exposition aux radiations</t>
-  </si>
-  <si>
-    <t>Event.partOf</t>
-  </si>
-  <si>
-    <t>Varies by domain</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=FLFS].target</t>
-  </si>
-  <si>
-    <t>Observation.partOf:imagingStudyRef</t>
-  </si>
-  <si>
-    <t>imagingStudyRef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-imaging-study-document|0.1.0)
-</t>
-  </si>
-  <si>
-    <t>Imaging study associé à cette exposition aux radiations</t>
-  </si>
-  <si>
-    <t>Observation.partOf:medicationAdministrationRef</t>
-  </si>
-  <si>
-    <t>medicationAdministrationRef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-administration-document|0.1.0)
-</t>
-  </si>
-  <si>
-    <t>Référence à l'administration du radiopharmaceutique associée à cette exposition aux radiations</t>
-  </si>
-  <si>
-    <t>Observation.status</t>
-  </si>
-  <si>
-    <t>registered | preliminary | final | amended +</t>
-  </si>
-  <si>
-    <t>The status of the result value.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
-  </si>
-  <si>
-    <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
-  </si>
-  <si>
-    <t>Codes providing the status of an observation.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.status</t>
-  </si>
-  <si>
-    <t>&lt; 445584004 |Report by finality status|</t>
-  </si>
-  <si>
-    <t>OBX-11</t>
-  </si>
-  <si>
-    <t>status  Amended &amp; Final are differentiated by whether it is the subject of a ControlAct event with a type of "revise"</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>Observation.category</t>
-  </si>
-  <si>
-    <t>Classification of  type of observation</t>
-  </si>
-  <si>
-    <t>A code that classifies the general type of observation being made.</t>
-  </si>
-  <si>
-    <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
-  </si>
-  <si>
-    <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name
-</t>
-  </si>
-  <si>
-    <t>Type of observation (code / type)</t>
-  </si>
-  <si>
-    <t>Describes what was observed. Sometimes this is called the observation "name".</t>
-  </si>
-  <si>
-    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="73569-6"/&gt;
-    &lt;display value="Exposition aux rayonnements et informations de radioprotection"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>116680003 |Is a|</t>
-  </si>
-  <si>
-    <t>Observation.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-document|0.1.0)
-</t>
-  </si>
-  <si>
-    <t>Patient exposé aux radiations</t>
-  </si>
-  <si>
-    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
-  </si>
-  <si>
-    <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
-  </si>
-  <si>
-    <t>Observations have no value if you don't know who or what they're about.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>PID-3</t>
-  </si>
-  <si>
-    <t>participation[typeCode=RTGT]</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>Observation.focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>What the observation is about, when it is not about the subject of record</t>
-  </si>
-  <si>
-    <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
-  </si>
-  <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
-  </si>
-  <si>
-    <t>participation[typeCode=SBJ]</t>
-  </si>
-  <si>
-    <t>Observation.encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Context
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
-  </si>
-  <si>
-    <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
-  </si>
-  <si>
-    <t>Event.context</t>
-  </si>
-  <si>
-    <t>PV1</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occurrence
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date de début de l'exposition aux radiations</t>
-  </si>
-  <si>
-    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
-  </si>
-  <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
-  </si>
-  <si>
-    <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>Observation.issued</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>Date/Time this version was made available</t>
-  </si>
-  <si>
-    <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
-  </si>
-  <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
-  </si>
-  <si>
-    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Observation.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Who is responsible for the observation</t>
-  </si>
-  <si>
-    <t>Who was responsible for asserting the observed value as "true".</t>
-  </si>
-  <si>
-    <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
-  </si>
-  <si>
     <t>closed</t>
   </si>
   <si>
@@ -1524,9 +1391,6 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
@@ -1540,92 +1404,6 @@
   </si>
   <si>
     <t>718497002 |Inherent location|</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.id</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension:precisionTopographique</t>
-  </si>
-  <si>
-    <t>precisionTopographique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {procedure-targetBodyStructure|5.3.0}
-</t>
-  </si>
-  <si>
-    <t>Modificateurs topographiques</t>
-  </si>
-  <si>
-    <t>The target body site used for this procedure.  Multiple locations are allowed.</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension:precisionTopographique.id</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension.id</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension:precisionTopographique.extension</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension:precisionTopographique.url</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/procedure-targetBodyStructure</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension:precisionTopographique.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-body-structure-document|0.1.0)
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.coding</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.text</t>
   </si>
   <si>
     <t>Observation.method</t>
@@ -1908,11 +1686,11 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-imaging-study-document|0.1.0)
 </t>
   </si>
   <si>
-    <t>Related measurements the observation is made from</t>
+    <t>Étude d'imagerie à partir de laquelle cette observation est dérivée</t>
   </si>
   <si>
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
@@ -2328,11 +2106,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP84"/>
+  <dimension ref="A1:AP71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.78515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.5234375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="52.86328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="27.73046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -2341,7 +2119,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="167.8125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="189.53125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2350,16 +2128,16 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="81.2890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.3125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
@@ -3657,16 +3435,16 @@
         <v>82</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>150</v>
@@ -3684,36 +3462,34 @@
         <v>105</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AN11" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
+      <c r="A12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="B12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3732,17 +3508,17 @@
         <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3779,19 +3555,17 @@
         <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3806,19 +3580,19 @@
         <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>82</v>
@@ -3826,21 +3600,23 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
@@ -3849,19 +3625,21 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+      <c r="O13" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>82</v>
       </c>
@@ -3909,31 +3687,31 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3944,21 +3722,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
@@ -3970,17 +3748,15 @@
         <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -4017,31 +3793,31 @@
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>82</v>
@@ -4053,7 +3829,7 @@
         <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>82</v>
@@ -4064,46 +3840,44 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -4127,43 +3901,43 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="AC15" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AD15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AA15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>187</v>
-      </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -4172,10 +3946,10 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>82</v>
@@ -4186,10 +3960,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4212,20 +3986,18 @@
         <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>195</v>
-      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>82</v>
       </c>
@@ -4249,13 +4021,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4273,7 +4045,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4282,7 +4054,7 @@
         <v>93</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>105</v>
@@ -4294,10 +4066,10 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>188</v>
+        <v>136</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>82</v>
@@ -4308,10 +4080,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4331,18 +4103,20 @@
         <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -4367,13 +4141,13 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -4391,7 +4165,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4403,7 +4177,7 @@
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>82</v>
@@ -4415,7 +4189,7 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -4433,14 +4207,14 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -4449,19 +4223,19 @@
         <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>139</v>
+        <v>205</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>142</v>
+        <v>208</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4499,31 +4273,31 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4535,7 +4309,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4546,10 +4320,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4560,7 +4334,7 @@
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>82</v>
@@ -4572,20 +4346,18 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4633,13 +4405,13 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>82</v>
@@ -4654,10 +4426,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4668,21 +4440,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>82</v>
+        <v>218</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -4691,18 +4463,20 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>167</v>
+        <v>219</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>168</v>
+        <v>220</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4751,31 +4525,31 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>170</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>171</v>
+        <v>225</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4786,44 +4560,46 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>140</v>
+        <v>227</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>174</v>
+        <v>228</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4847,58 +4623,58 @@
         <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>82</v>
+        <v>231</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>82</v>
+        <v>232</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>82</v>
+        <v>234</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>171</v>
+        <v>237</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>82</v>
+        <v>238</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4906,10 +4682,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4920,7 +4696,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4929,22 +4705,22 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>107</v>
+        <v>240</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4969,13 +4745,13 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>82</v>
+        <v>246</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4993,13 +4769,13 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
@@ -5014,38 +4790,38 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>82</v>
@@ -5054,18 +4830,20 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>167</v>
+        <v>240</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5089,13 +4867,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -5113,10 +4891,10 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>93</v>
@@ -5128,30 +4906,30 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>82</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5171,21 +4949,19 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>113</v>
+        <v>176</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>238</v>
+        <v>177</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>239</v>
+        <v>178</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>240</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5194,7 +4970,7 @@
         <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>82</v>
@@ -5233,7 +5009,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>179</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5245,7 +5021,7 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -5254,10 +5030,10 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>243</v>
+        <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>244</v>
+        <v>180</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5268,21 +5044,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -5291,21 +5067,21 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>247</v>
+        <v>140</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5341,31 +5117,31 @@
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>186</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -5374,10 +5150,10 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>252</v>
+        <v>180</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5388,10 +5164,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5399,10 +5175,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -5414,19 +5190,19 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5463,25 +5239,23 @@
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
@@ -5496,10 +5270,10 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5510,18 +5284,20 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>93</v>
@@ -5536,19 +5312,19 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>167</v>
+        <v>267</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5597,13 +5373,13 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -5618,10 +5394,10 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5632,10 +5408,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5655,23 +5431,19 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>107</v>
+        <v>176</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>274</v>
+        <v>177</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5680,10 +5452,10 @@
         <v>82</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>82</v>
@@ -5719,7 +5491,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>280</v>
+        <v>179</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5731,7 +5503,7 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5740,10 +5512,10 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>282</v>
+        <v>180</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5754,21 +5526,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5777,19 +5549,19 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>285</v>
+        <v>140</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>286</v>
+        <v>183</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>287</v>
+        <v>142</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5803,7 +5575,7 @@
         <v>82</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>82</v>
@@ -5827,31 +5599,31 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>186</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5860,10 +5632,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>291</v>
+        <v>180</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5874,10 +5646,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5900,22 +5672,26 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>294</v>
+        <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>82</v>
@@ -5957,7 +5733,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5978,10 +5754,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5992,10 +5768,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6018,16 +5794,16 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>302</v>
+        <v>176</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6077,7 +5853,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6098,10 +5874,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6112,24 +5888,24 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
@@ -6138,24 +5914,24 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>311</v>
+        <v>113</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>82</v>
@@ -6185,23 +5961,25 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
@@ -6210,16 +5988,16 @@
         <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6230,23 +6008,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -6258,17 +6034,17 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>321</v>
+        <v>176</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6317,13 +6093,13 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
@@ -6332,16 +6108,16 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6352,21 +6128,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>324</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G34" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -6378,18 +6154,20 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6425,25 +6203,25 @@
         <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
@@ -6452,16 +6230,16 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6470,28 +6248,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>324</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6500,18 +6276,20 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>336</v>
+        <v>176</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6559,13 +6337,13 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
@@ -6574,16 +6352,16 @@
         <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6594,20 +6372,18 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>324</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>93</v>
@@ -6622,18 +6398,20 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="O36" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="L36" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6681,13 +6459,13 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
@@ -6696,19 +6474,19 @@
         <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6716,10 +6494,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6727,35 +6505,33 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>113</v>
+        <v>346</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6779,13 +6555,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6803,13 +6579,13 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>82</v>
@@ -6818,19 +6594,19 @@
         <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AM37" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>352</v>
-      </c>
       <c r="AO37" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6838,21 +6614,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6861,22 +6637,22 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>191</v>
+        <v>353</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6901,13 +6677,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6925,13 +6701,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6940,19 +6716,19 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6960,14 +6736,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6986,7 +6762,7 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>191</v>
+        <v>364</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>365</v>
@@ -7008,7 +6784,7 @@
         <v>82</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>82</v>
@@ -7023,13 +6799,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -7047,10 +6823,10 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>93</v>
@@ -7062,30 +6838,30 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AP39" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AL39" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>379</v>
-      </c>
       <c r="B40" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7093,13 +6869,13 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
@@ -7108,20 +6884,18 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7169,7 +6943,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7184,19 +6958,19 @@
         <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -7204,10 +6978,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7215,13 +6989,13 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
@@ -7230,18 +7004,18 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7277,19 +7051,17 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7304,44 +7076,46 @@
         <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="D42" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
@@ -7350,19 +7124,17 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7411,13 +7183,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -7426,44 +7198,44 @@
         <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>82</v>
@@ -7472,19 +7244,19 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7533,7 +7305,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7542,36 +7314,36 @@
         <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>82</v>
+        <v>402</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7591,21 +7363,23 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>418</v>
+        <v>240</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7629,13 +7403,13 @@
         <v>82</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -7653,7 +7427,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7662,7 +7436,7 @@
         <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>105</v>
@@ -7674,13 +7448,13 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>422</v>
+        <v>136</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7688,43 +7462,45 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>426</v>
+        <v>240</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="O45" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7749,29 +7525,31 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AC45" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7786,65 +7564,65 @@
         <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>82</v>
+        <v>424</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="O46" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7893,7 +7671,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7908,30 +7686,30 @@
         <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7939,35 +7717,33 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>440</v>
+        <v>240</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -7991,13 +7767,11 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -8015,7 +7789,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8024,7 +7798,7 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>105</v>
@@ -8033,27 +7807,27 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8076,19 +7850,19 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8113,13 +7887,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>196</v>
+        <v>255</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8137,7 +7911,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8146,7 +7920,7 @@
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>105</v>
@@ -8158,10 +7932,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>136</v>
+        <v>452</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8172,21 +7946,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>460</v>
+        <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8198,20 +7972,18 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>191</v>
+        <v>455</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8235,13 +8007,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>466</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8259,13 +8031,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -8277,27 +8049,27 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>470</v>
+        <v>462</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8308,10 +8080,10 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
@@ -8320,20 +8092,18 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>476</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8381,13 +8151,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -8399,27 +8169,27 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>82</v>
+        <v>471</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8427,13 +8197,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>82</v>
@@ -8442,18 +8212,20 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>191</v>
+        <v>473</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>476</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8477,13 +8249,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8501,45 +8273,45 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AG51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>486</v>
-      </c>
       <c r="AN51" t="s" s="2">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>488</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8562,13 +8334,13 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8619,7 +8391,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8643,7 +8415,7 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8654,10 +8426,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8686,7 +8458,7 @@
         <v>140</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>142</v>
@@ -8727,19 +8499,19 @@
         <v>82</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8763,7 +8535,7 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8772,46 +8544,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I54" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I54" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>493</v>
+        <v>139</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8859,7 +8633,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>177</v>
+        <v>487</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8883,7 +8657,7 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8894,10 +8668,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8920,13 +8694,13 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>167</v>
+        <v>489</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>168</v>
+        <v>490</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>169</v>
+        <v>491</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8977,7 +8751,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>170</v>
+        <v>488</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8986,10 +8760,10 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8998,10 +8772,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>82</v>
+        <v>493</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>171</v>
+        <v>494</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -9012,10 +8786,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9026,7 +8800,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -9038,13 +8812,13 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>139</v>
+        <v>489</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9083,31 +8857,31 @@
         <v>82</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>177</v>
+        <v>495</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -9116,10 +8890,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>82</v>
+        <v>493</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9130,10 +8904,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9141,7 +8915,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>93</v>
@@ -9156,24 +8930,26 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>107</v>
+        <v>240</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>502</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>507</v>
+        <v>82</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>82</v>
@@ -9191,13 +8967,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>82</v>
+        <v>505</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9215,10 +8991,10 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>93</v>
@@ -9227,19 +9003,19 @@
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>82</v>
+        <v>507</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>136</v>
+        <v>426</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9250,10 +9026,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9261,10 +9037,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9276,16 +9052,20 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9309,13 +9089,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>82</v>
+        <v>513</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>82</v>
+        <v>514</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9333,13 +9113,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9351,13 +9131,13 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>82</v>
+        <v>507</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>136</v>
+        <v>426</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9382,7 +9162,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9391,22 +9171,20 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>207</v>
+        <v>516</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>208</v>
+        <v>517</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>211</v>
+        <v>519</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9455,13 +9233,13 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>212</v>
+        <v>515</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
@@ -9476,10 +9254,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>214</v>
+        <v>520</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9490,10 +9268,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9513,23 +9291,19 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>265</v>
+        <v>522</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9577,7 +9351,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>269</v>
+        <v>521</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9598,10 +9372,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>270</v>
+        <v>493</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>271</v>
+        <v>524</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9612,10 +9386,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9626,7 +9400,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9635,23 +9409,21 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>191</v>
+        <v>526</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>521</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9675,13 +9447,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>523</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9699,13 +9471,13 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
@@ -9720,10 +9492,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9734,10 +9506,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9748,7 +9520,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9757,19 +9529,19 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9819,13 +9591,13 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
@@ -9837,27 +9609,27 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9868,30 +9640,32 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J63" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K63" t="s" s="2">
-        <v>536</v>
+        <v>473</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>541</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>542</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9939,13 +9713,13 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
@@ -9957,27 +9731,27 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>540</v>
+        <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>543</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9988,7 +9762,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -10000,20 +9774,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>545</v>
+        <v>176</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>546</v>
+        <v>177</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>549</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10061,19 +9831,19 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>544</v>
+        <v>179</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>550</v>
+        <v>82</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -10082,10 +9852,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>551</v>
+        <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>552</v>
+        <v>180</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10096,21 +9866,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -10122,15 +9892,17 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10179,19 +9951,19 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10203,7 +9975,7 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10214,14 +9986,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>138</v>
+        <v>484</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10234,24 +10006,26 @@
         <v>82</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>140</v>
+        <v>485</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>174</v>
+        <v>486</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="O66" s="2"/>
+      <c r="O66" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10299,7 +10073,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>177</v>
+        <v>487</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10323,7 +10097,7 @@
         <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10334,45 +10108,45 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>556</v>
+        <v>82</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>142</v>
+        <v>551</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10397,13 +10171,11 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>82</v>
+        <v>552</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10421,45 +10193,45 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>82</v>
+        <v>553</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>82</v>
+        <v>260</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>136</v>
+        <v>261</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10467,31 +10239,35 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10539,7 +10315,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10548,7 +10324,7 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>564</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10557,27 +10333,27 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>82</v>
+        <v>558</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>565</v>
+        <v>404</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>566</v>
+        <v>405</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10600,16 +10376,20 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="L69" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+      <c r="N69" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10633,13 +10413,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10657,7 +10437,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10666,7 +10446,7 @@
         <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>564</v>
+        <v>414</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10678,10 +10458,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>565</v>
+        <v>136</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>570</v>
+        <v>415</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10692,21 +10472,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10718,19 +10498,19 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>572</v>
+        <v>418</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>573</v>
+        <v>419</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>574</v>
+        <v>420</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>575</v>
+        <v>421</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10755,13 +10535,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>117</v>
+        <v>199</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>576</v>
+        <v>422</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>577</v>
+        <v>423</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10779,13 +10559,13 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
@@ -10797,27 +10577,27 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>578</v>
+        <v>424</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>579</v>
+        <v>425</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>469</v>
+        <v>426</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10840,19 +10620,19 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>191</v>
+        <v>83</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>581</v>
+        <v>565</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>583</v>
+        <v>476</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>584</v>
+        <v>477</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10877,13 +10657,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>585</v>
+        <v>82</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>586</v>
+        <v>82</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10901,7 +10681,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10919,1591 +10699,23 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>578</v>
+        <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>579</v>
+        <v>479</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="P79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="P80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y80" s="2"/>
-      <c r="Z80" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="P81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP84" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP84">
+  <autoFilter ref="A1:AP71">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12513,7 +10725,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI83">
+  <conditionalFormatting sqref="A2:AI70">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T07:33:45+00:00</t>
+    <t>2026-09-30T20:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1744,7 +1744,7 @@
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-quantite-exposition-rayonnements-cisis|20260716085851</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-quantite-exposition-rayonnements-cisis|20260916095452</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR 
--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:06:50+00:00</t>
+    <t>2026-10-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:49:37+00:00</t>
+    <t>2026-10-01T13:34:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:34:48+00:00</t>
+    <t>2026-10-05T07:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
